--- a/assetcore/public/import_templates/04_danh_sach_phu_tung.xlsx
+++ b/assetcore/public/import_templates/04_danh_sach_phu_tung.xlsx
@@ -550,7 +550,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Danh sách phụ tùng  |  Điền dữ liệu từ hàng 5 trở xuống. Cột đỏ = bắt buộc. Không xóa hàng 2-4.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Danh sách phụ tùng  |  Điền dữ liệu từ HÀNG 6 trở xuống (hàng 5 là ví dụ mẫu, hệ thống bỏ qua). Cột đỏ = bắt buộc. Không xoá/không sửa hàng 1-5. Cột tham chiếu (danh mục, khoa phòng, vị trí, model, nhà cung cấp) điền TÊN, không điền mã.</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Electrical / Mechanical / Consumable / Filter / Battery / Sensor / Other</t>
+          <t>Điện / Cơ khí / Tiêu hao / Bộ lọc / Pin, ắc-quy / Cảm biến / Khác.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Tên NCC ưu tiên (khớp file 02 / sheet 'Nhà cung cấp').</t>
+          <t>Tên nhà cung cấp ưu tiên, khớp file 02 / sheet 'Nhà cung cấp'. Điền TÊN, KHÔNG điền mã hệ thống.</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Điện</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2567,13 +2567,13 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C5:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
-      <formula1>"Electrical,Mechanical,Consumable,Filter,Battery,Sensor,Other"</formula1>
+    <dataValidation sqref="C6:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+      <formula1>"Điện,Cơ khí,Tiêu hao,Bộ lọc,Pin/Ắc-quy,Cảm biến,Khác"</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="M6:M105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="O5:O105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="O6:O105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>

--- a/assetcore/public/import_templates/04_danh_sach_phu_tung.xlsx
+++ b/assetcore/public/import_templates/04_danh_sach_phu_tung.xlsx
@@ -2567,13 +2567,13 @@
     <mergeCell ref="A1:O1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="C6:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Điện,Cơ khí,Tiêu hao,Bộ lọc,Pin/Ắc-quy,Cảm biến,Khác"</formula1>
     </dataValidation>
-    <dataValidation sqref="M6:M105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="M6:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
-    <dataValidation sqref="O6:O105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="O6:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
